--- a/output/raw_orders.xlsx
+++ b/output/raw_orders.xlsx
@@ -559,7 +559,9 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>Bob</t>
@@ -598,9 +600,7 @@
           <t>completed</t>
         </is>
       </c>
-      <c r="E8" t="n">
-        <v>45</v>
-      </c>
+      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>210</v>
+        <v>275.5</v>
       </c>
     </row>
     <row r="11">

--- a/output/raw_orders.xlsx
+++ b/output/raw_orders.xlsx
@@ -600,7 +600,9 @@
           <t>completed</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
